--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet basé sur le CodeSystem EDQM fourni par SMT. classe PDF (forme galénique).</t>
+    <t>ValueSet basé sur le CodeSystem EDQM fourni par SMT.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,16 +99,10 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>concept</t>
-  </si>
-  <si>
-    <t>is-a</t>
-  </si>
-  <si>
-    <t>PDF</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
@@ -381,7 +375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -390,40 +384,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
         <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
